--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/nov-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/nov-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/nov-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/nov-2025.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MULCHEN DEPTO COMUNAL</t>
+          <t>I MUNICIPALIDAD DE MULCHEN</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3106,17 +3106,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MOP Dirección General de Concesiones</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARRO</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10312,12 +10312,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10505,7 +10505,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10556,17 +10556,17 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Superintendencia de Insolvencia y Reemprendimiento</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Superintendencia de Insolvencia y Reemprendimiento</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MULCHEN DEPTO COMUNAL</t>
+          <t>I MUNICIPALIDAD DE MULCHEN</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE MULCHEN DIRECCION DE SALUD MUNICIPAL</t>
+          <t>I MUNICIPALIDAD DE MULCHEN</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCAC</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCAC</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14098,7 +14098,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección General</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14769,7 +14769,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DIRECTORIO DE TRANSPORTE DE SANTIAGO</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14891,12 +14891,12 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Santa Rosa</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/nov-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/nov-2025.xlsx
@@ -684,7 +684,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1058,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1123,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1188,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1253,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1318,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1444,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1509,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1574,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1700,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1765,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1952,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2139,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2204,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2330,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2456,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2643,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2830,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2895,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2960,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3025,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3090,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3155,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3220,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3285,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3411,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3476,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3541,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3606,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3671,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3736,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3862,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3927,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3992,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4057,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4122,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4187,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4313,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4378,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4443,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4508,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4573,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4638,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4703,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4829,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4894,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5020,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5085,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5272,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5337,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5463,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5528,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5593,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5658,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5723,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5788,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5914,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6040,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6105,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6353,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6418,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6483,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6548,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6613,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6739,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6804,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6930,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6995,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7121,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7186,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7251,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7316,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7381,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7446,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7572,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7637,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7702,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7828,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7893,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7958,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8023,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8210,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8336,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8401,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8466,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8592,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8657,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8722,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8787,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8852,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8917,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8982,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9047,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9173,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9238,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9303,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9110,7 +9498,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9171,7 +9563,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9232,7 +9628,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9293,7 +9693,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9354,7 +9758,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9476,7 +9884,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9659,7 +10071,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9720,7 +10136,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9781,7 +10201,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9842,7 +10266,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9964,7 +10392,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10025,7 +10457,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10086,7 +10522,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10208,7 +10648,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10269,7 +10713,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10391,7 +10839,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10452,7 +10904,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10513,7 +10969,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10574,7 +11034,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10635,7 +11099,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10696,7 +11164,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10757,7 +11229,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10818,7 +11294,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10879,7 +11359,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10940,7 +11424,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11062,7 +11550,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11123,7 +11615,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11184,7 +11680,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11245,7 +11745,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11306,7 +11810,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11611,7 +12119,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11672,7 +12184,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11794,7 +12310,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11855,7 +12375,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11977,7 +12501,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12038,7 +12566,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12099,7 +12631,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12160,7 +12696,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12221,7 +12761,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12282,7 +12826,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12343,7 +12891,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12404,7 +12956,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12465,7 +13021,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12526,7 +13086,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12770,7 +13334,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12957,7 +13525,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13018,7 +13590,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13140,7 +13716,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13201,7 +13781,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13262,7 +13846,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13323,7 +13911,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13384,7 +13976,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13445,7 +14041,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13506,7 +14106,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13567,7 +14171,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13628,7 +14236,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13689,7 +14301,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13750,7 +14366,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13811,7 +14431,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13872,7 +14496,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13933,7 +14561,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13994,7 +14626,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14055,7 +14691,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14116,7 +14756,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14177,7 +14821,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14238,7 +14886,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14299,7 +14951,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14360,7 +15016,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14665,7 +15325,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14726,7 +15390,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14848,7 +15516,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14909,7 +15581,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14970,7 +15646,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15031,7 +15711,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15092,7 +15776,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15153,7 +15841,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15214,7 +15906,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15336,7 +16032,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15397,7 +16097,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15519,7 +16223,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15580,7 +16288,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15702,7 +16414,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
